--- a/Data/Terminator_Strength-250328.xlsx
+++ b/Data/Terminator_Strength-250328.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{79448CCA-0E39-4660-8427-3946E7B72172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4887E82-8CA5-4893-825B-99665F903A0C}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{79448CCA-0E39-4660-8427-3946E7B72172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBAC6E1C-BCC5-4D70-9418-5FD1650B5026}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C2D8DAA-8564-469B-976C-6A669E948518}"/>
   </bookViews>
   <sheets>
-    <sheet name="RFP" sheetId="1" r:id="rId1"/>
-    <sheet name="GFP" sheetId="2" r:id="rId2"/>
-    <sheet name="OD600" sheetId="3" r:id="rId3"/>
+    <sheet name="PlateMap" sheetId="4" r:id="rId1"/>
+    <sheet name="RFP" sheetId="1" r:id="rId2"/>
+    <sheet name="GFP" sheetId="2" r:id="rId3"/>
+    <sheet name="OD600" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="115">
   <si>
     <t>A1</t>
   </si>
@@ -326,6 +327,63 @@
   </si>
   <si>
     <t>H12</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>TT7hyb1_pin</t>
+  </si>
+  <si>
+    <t>40bp_spacer_pin</t>
+  </si>
+  <si>
+    <t>20bp_spacer</t>
+  </si>
+  <si>
+    <t>J23015_pin</t>
+  </si>
+  <si>
+    <t>TT7hyb1</t>
+  </si>
+  <si>
+    <t>TT7hyb6</t>
+  </si>
+  <si>
+    <t>40bp_spacer</t>
+  </si>
+  <si>
+    <t>20bp_spacer_pin</t>
+  </si>
+  <si>
+    <t>J23105</t>
   </si>
 </sst>
 </file>
@@ -378,6 +436,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -696,6 +758,196 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A26F40-ACFF-43C0-B8AA-38AD84C9BE83}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326CB377-79BF-45B6-A989-B9343D301CCA}">
   <dimension ref="A1:CR2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1282,7 +1534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A025767F-8B48-47C8-910C-B171ADF2133E}">
   <dimension ref="A1:CR2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1869,7 +2121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3F781A-9B12-469E-8AA1-374254F0F419}">
   <dimension ref="A1:CR2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
